--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126360958</v>
+        <v>126361091</v>
       </c>
       <c r="B3" t="n">
         <v>57656</v>
@@ -813,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598373</v>
+        <v>598356</v>
       </c>
       <c r="R3" t="n">
-        <v>6925426</v>
+        <v>6925424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126361091</v>
+        <v>126360958</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598356</v>
+        <v>598373</v>
       </c>
       <c r="R4" t="n">
-        <v>6925424</v>
+        <v>6925426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126361091</v>
+        <v>126360958</v>
       </c>
       <c r="B3" t="n">
         <v>57656</v>
@@ -813,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598356</v>
+        <v>598373</v>
       </c>
       <c r="R3" t="n">
-        <v>6925424</v>
+        <v>6925426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126360958</v>
+        <v>126361091</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598373</v>
+        <v>598356</v>
       </c>
       <c r="R4" t="n">
-        <v>6925426</v>
+        <v>6925424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126360836</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126360958</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126361091</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126360738</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126360900</v>
       </c>
       <c r="B6" t="n">
-        <v>98388</v>
+        <v>98397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126360836</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126360958</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126361091</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126360738</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126360836</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126360958</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126361091</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126360738</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126360836</v>
+        <v>126360738</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598373</v>
+        <v>598412</v>
       </c>
       <c r="R2" t="n">
-        <v>6925419</v>
+        <v>6925364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126360958</v>
+        <v>126360836</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>598373</v>
       </c>
       <c r="R3" t="n">
-        <v>6925426</v>
+        <v>6925419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126361091</v>
+        <v>126360958</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598356</v>
+        <v>598373</v>
       </c>
       <c r="R4" t="n">
-        <v>6925424</v>
+        <v>6925426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126360738</v>
+        <v>126361091</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598412</v>
+        <v>598356</v>
       </c>
       <c r="R5" t="n">
-        <v>6925364</v>
+        <v>6925424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
         <v>126360900</v>
       </c>
       <c r="B6" t="n">
-        <v>98397</v>
+        <v>99155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39929-2021 artfynd.xlsx
+++ b/artfynd/A 39929-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361091</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360900</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>